--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_27_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_27_9.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9926971179332557</v>
+        <v>0.9996999105362713</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7110860737853579</v>
+        <v>0.6233340202726746</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9447660913856289</v>
+        <v>0.9988038216233187</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9850762199004843</v>
+        <v>0.9997864047334063</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9810767585909181</v>
+        <v>0.9993092225722835</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04883440600699923</v>
+        <v>0.0001781460688592494</v>
       </c>
       <c r="H2" t="n">
-        <v>1.931968754923618</v>
+        <v>0.2236051966892406</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08977567254821567</v>
+        <v>0.0009502825336893917</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2141430340966905</v>
+        <v>0.0001618038103664505</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1519592883555591</v>
+        <v>0.0005560432526190481</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2468594185244284</v>
+        <v>0.005341665135651334</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2209850809602296</v>
+        <v>0.01334713710348588</v>
       </c>
       <c r="N2" t="n">
-        <v>1.002503845280027</v>
+        <v>1.00021182785675</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2303928733588875</v>
+        <v>0.013915352362364</v>
       </c>
       <c r="P2" t="n">
-        <v>194.0386403468415</v>
+        <v>133.2658134652419</v>
       </c>
       <c r="Q2" t="n">
-        <v>308.6129678844523</v>
+        <v>203.9606113075975</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9928152497827334</v>
+        <v>0.9997014376044978</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7110674365697746</v>
+        <v>0.6233129333353948</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9457247444218845</v>
+        <v>0.9988140615978259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9853328957286412</v>
+        <v>0.9997835553210338</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9814030823457439</v>
+        <v>0.9993129349786309</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04804445778559439</v>
+        <v>0.0001772395351940384</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93209338207004</v>
+        <v>0.2236177148061182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08821750432819886</v>
+        <v>0.0009421475689472701</v>
       </c>
       <c r="J3" t="n">
-        <v>0.210459963168663</v>
+        <v>0.0001639623122215071</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1493388110026126</v>
+        <v>0.0005530549405843887</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2457983763826004</v>
+        <v>0.005363131853593116</v>
       </c>
       <c r="M3" t="n">
-        <v>0.219190460069763</v>
+        <v>0.01331313393585592</v>
       </c>
       <c r="N3" t="n">
-        <v>1.002463342931634</v>
+        <v>1.000210749926237</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2285218517417364</v>
+        <v>0.01387990160949177</v>
       </c>
       <c r="P3" t="n">
-        <v>194.0712569857397</v>
+        <v>133.2760168682058</v>
       </c>
       <c r="Q3" t="n">
-        <v>308.6455845233505</v>
+        <v>203.9708147105615</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9929442714901953</v>
+        <v>0.9997031051035457</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7110452029911631</v>
+        <v>0.6232894026987692</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9467789598873434</v>
+        <v>0.9988253791084362</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9856154370911385</v>
+        <v>0.9997803598420317</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9817622094227295</v>
+        <v>0.9993170161729827</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04718168903370648</v>
+        <v>0.0001762496357270335</v>
       </c>
       <c r="H4" t="n">
-        <v>1.932242058112591</v>
+        <v>0.2236316836084898</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08650401156991738</v>
+        <v>0.0009331565749053719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2064057447186782</v>
+        <v>0.0001663829682909365</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1464549131614243</v>
+        <v>0.0005497697715981542</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2446268313739413</v>
+        <v>0.005386872860492917</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2172134642090736</v>
+        <v>0.01327590432803105</v>
       </c>
       <c r="N4" t="n">
-        <v>1.002419106917647</v>
+        <v>1.000209572868085</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2264606910743118</v>
+        <v>0.01384108706018588</v>
       </c>
       <c r="P4" t="n">
-        <v>194.1074988117232</v>
+        <v>133.287218366142</v>
       </c>
       <c r="Q4" t="n">
-        <v>308.681826349334</v>
+        <v>203.9820162084976</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9930849250953848</v>
+        <v>0.9997049082279559</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7110186210332126</v>
+        <v>0.6232630072984361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9479376133169471</v>
+        <v>0.9988377986731404</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9859261533814702</v>
+        <v>0.9997767930708547</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9821570884571759</v>
+        <v>0.9993214658706009</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04624113772815382</v>
+        <v>0.0001751792231862075</v>
       </c>
       <c r="H5" t="n">
-        <v>1.932419811787806</v>
+        <v>0.2236473530583494</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08462076822353017</v>
+        <v>0.0009232900736840847</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2019472409943416</v>
+        <v>0.0001690848875626561</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1432839164086054</v>
+        <v>0.0005461879748608874</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2433243680710825</v>
+        <v>0.005413193593759563</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2150375263254156</v>
+        <v>0.01323552882155479</v>
       </c>
       <c r="N5" t="n">
-        <v>1.00237088282444</v>
+        <v>1.000208300074384</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2241921190101341</v>
+        <v>0.01379899268481011</v>
       </c>
       <c r="P5" t="n">
-        <v>194.1477709001462</v>
+        <v>133.2994019512281</v>
       </c>
       <c r="Q5" t="n">
-        <v>308.722098437757</v>
+        <v>203.9941997935837</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9932379129155869</v>
+        <v>0.9997068567963568</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7109868071866103</v>
+        <v>0.6232336859668015</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9492097377506327</v>
+        <v>0.9988514499254576</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9862675215000591</v>
+        <v>0.9997727913997276</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9825908225470877</v>
+        <v>0.9993263200491957</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04521810747001782</v>
+        <v>0.0001740224688096153</v>
       </c>
       <c r="H6" t="n">
-        <v>1.932632551126524</v>
+        <v>0.2236647594674232</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08255309223491798</v>
+        <v>0.0009124450802508852</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1970489106671013</v>
+        <v>0.0001721162545330016</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1398009019390591</v>
+        <v>0.0005422805900124696</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2418749819102757</v>
+        <v>0.005442213328137723</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2126454971778566</v>
+        <v>0.01319175760881071</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002318429857513</v>
+        <v>1.000206924614336</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2216982562295806</v>
+        <v>0.01375335804092061</v>
       </c>
       <c r="P6" t="n">
-        <v>194.1925153292441</v>
+        <v>133.3126522719934</v>
       </c>
       <c r="Q6" t="n">
-        <v>308.7668428668549</v>
+        <v>204.007450114349</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9934037332177539</v>
+        <v>0.9997089560984886</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7109486322826494</v>
+        <v>0.6232008713308417</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9506029697809323</v>
+        <v>0.9988664316551609</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9866418895166295</v>
+        <v>0.9997683138450741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9830662828995017</v>
+        <v>0.9993316059485543</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04410926634589551</v>
+        <v>0.0001727762323790538</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93288782688509</v>
+        <v>0.2236842396528475</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08028857129708014</v>
+        <v>0.0009005431128361566</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1916770610148982</v>
+        <v>0.0001755081152966371</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1359828131015183</v>
+        <v>0.0005380256903090024</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2402679977845808</v>
+        <v>0.005474255418497743</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2100220615694825</v>
+        <v>0.01314443731694338</v>
       </c>
       <c r="N7" t="n">
-        <v>1.002261577182484</v>
+        <v>1.000205442754008</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2189631355360977</v>
+        <v>0.01370402322626199</v>
       </c>
       <c r="P7" t="n">
-        <v>194.2421707947592</v>
+        <v>133.3270265103141</v>
       </c>
       <c r="Q7" t="n">
-        <v>308.81649833237</v>
+        <v>204.0218243526698</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9935828546425036</v>
+        <v>0.9997112019906174</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7109026152283587</v>
+        <v>0.6231641358139577</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9521267448281863</v>
+        <v>0.998882830129144</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9870517534115009</v>
+        <v>0.9997632952366411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9835866756973247</v>
+        <v>0.9993373366596836</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04291148055381593</v>
+        <v>0.0001714429737939704</v>
       </c>
       <c r="H8" t="n">
-        <v>1.93319554313902</v>
+        <v>0.2237060474425615</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0778118693378814</v>
+        <v>0.000887515638247779</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1857958769295533</v>
+        <v>0.0001793098379666352</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1318039032882873</v>
+        <v>0.0005334127381072071</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2384813416233741</v>
+        <v>0.005509665814688283</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2071508642362274</v>
+        <v>0.0130936234020217</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00220016412257</v>
+        <v>1.000203857418388</v>
       </c>
       <c r="O8" t="n">
-        <v>0.215969705388168</v>
+        <v>0.01365104605778279</v>
       </c>
       <c r="P8" t="n">
-        <v>194.2972317537456</v>
+        <v>133.3425197219486</v>
       </c>
       <c r="Q8" t="n">
-        <v>308.8715592913564</v>
+        <v>204.0373175643042</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9937756718061976</v>
+        <v>0.99971359423618</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7108472073102796</v>
+        <v>0.6231230022569918</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9537909585084673</v>
+        <v>0.9989007584718852</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9874998430673588</v>
+        <v>0.9997576607663738</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9841554303200339</v>
+        <v>0.9993435323339496</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04162211129235256</v>
+        <v>0.0001700228334883222</v>
       </c>
       <c r="H9" t="n">
-        <v>1.933566056142345</v>
+        <v>0.2237304660988536</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07510690229572836</v>
+        <v>0.0008732727867658654</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1793661870109862</v>
+        <v>0.0001835780915341277</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1272366335564563</v>
+        <v>0.0005284255125077985</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2365029342848639</v>
+        <v>0.005548698710991126</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2040149781078648</v>
+        <v>0.0130392804053108</v>
       </c>
       <c r="N9" t="n">
-        <v>1.002134055380732</v>
+        <v>1.000202168774461</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2127003180951418</v>
+        <v>0.01359438956719639</v>
       </c>
       <c r="P9" t="n">
-        <v>194.3582474629433</v>
+        <v>133.3591556305925</v>
       </c>
       <c r="Q9" t="n">
-        <v>308.9325750005541</v>
+        <v>204.0539534729481</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9939820781386716</v>
+        <v>0.9997161289438953</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7107801725974252</v>
+        <v>0.6230770646923544</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9556029190744111</v>
+        <v>0.9989203234950201</v>
       </c>
       <c r="E10" t="n">
-        <v>0.987988361675865</v>
+        <v>0.999751351988265</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9847752807076589</v>
+        <v>0.9993502192333825</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04024187119668527</v>
+        <v>0.0001685181214949161</v>
       </c>
       <c r="H10" t="n">
-        <v>1.934014317575869</v>
+        <v>0.2237577366216218</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0721617915382374</v>
+        <v>0.0008577297037952919</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1723563774090882</v>
+        <v>0.000188357150326184</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1222590495498821</v>
+        <v>0.0005230428738148296</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2343060128329441</v>
+        <v>0.005591611687970505</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2006037666562751</v>
+        <v>0.01298145298088454</v>
       </c>
       <c r="N10" t="n">
-        <v>1.002063287495313</v>
+        <v>1.000200379569015</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2091438843098768</v>
+        <v>0.01353410030959303</v>
       </c>
       <c r="P10" t="n">
-        <v>194.4256945067202</v>
+        <v>133.3769345359812</v>
       </c>
       <c r="Q10" t="n">
-        <v>309.0000220443311</v>
+        <v>204.0717323783369</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9942018517714628</v>
+        <v>0.999718792655373</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7106989752849507</v>
+        <v>0.6230255410732178</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9575711693284803</v>
+        <v>0.9989416703116644</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9885198011779016</v>
+        <v>0.9997442274758266</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9854492827134254</v>
+        <v>0.9993574000840811</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03877224390224573</v>
+        <v>0.0001669368272953403</v>
       </c>
       <c r="H11" t="n">
-        <v>1.934557284378266</v>
+        <v>0.2237883232676458</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06896265182976705</v>
+        <v>0.0008407711068148247</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1647306909780321</v>
+        <v>0.0001937541484803073</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1168466118531699</v>
+        <v>0.000517262627647566</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2318667192526641</v>
+        <v>0.00563907289411181</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1969066883126262</v>
+        <v>0.01292040352679978</v>
       </c>
       <c r="N11" t="n">
-        <v>1.001987936535498</v>
+        <v>1.00019849930209</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2052894136871315</v>
+        <v>0.0134704518538581</v>
       </c>
       <c r="P11" t="n">
-        <v>194.5001013033831</v>
+        <v>133.3957901935639</v>
       </c>
       <c r="Q11" t="n">
-        <v>309.0744288409939</v>
+        <v>204.0905880359195</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9944341950726806</v>
+        <v>0.9997215651063686</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7106004499376808</v>
+        <v>0.6229677065839965</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9597024143750017</v>
+        <v>0.9989648426972021</v>
       </c>
       <c r="E12" t="n">
-        <v>0.989096203094071</v>
+        <v>0.9997362380163165</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9861799441815439</v>
+        <v>0.9993650754841344</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03721856317715973</v>
+        <v>0.0001652909806207233</v>
       </c>
       <c r="H12" t="n">
-        <v>1.935216123829128</v>
+        <v>0.2238226563187674</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06549858487856949</v>
+        <v>0.000822362219252829</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1564598337042995</v>
+        <v>0.0001998063658919196</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1109791817272281</v>
+        <v>0.0005110842925723743</v>
       </c>
       <c r="L12" t="n">
-        <v>0.229162451986423</v>
+        <v>0.005691084580223208</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1929211320129543</v>
+        <v>0.01285655399478116</v>
       </c>
       <c r="N12" t="n">
-        <v>1.001908275975081</v>
+        <v>1.000196542277858</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2011341840045436</v>
+        <v>0.01340388411507468</v>
       </c>
       <c r="P12" t="n">
-        <v>194.581895264057</v>
+        <v>133.4156062366479</v>
       </c>
       <c r="Q12" t="n">
-        <v>309.1562228016678</v>
+        <v>204.1104040790035</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9946777615044422</v>
+        <v>0.9997244207870276</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7104807052006101</v>
+        <v>0.6229030413712533</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9620023207014524</v>
+        <v>0.9989899680734852</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9897192558333667</v>
+        <v>0.9997272490035363</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9869693666440034</v>
+        <v>0.9993732442868453</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03558983332644976</v>
+        <v>0.0001635957252225811</v>
       </c>
       <c r="H13" t="n">
-        <v>1.936016857437293</v>
+        <v>0.2238610443824435</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06176038053209517</v>
+        <v>0.0008024018130963191</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1475195784133913</v>
+        <v>0.0002066157701566487</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1046398832416282</v>
+        <v>0.0005045087916264838</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2261642145110278</v>
+        <v>0.005748281022296949</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1886526790863299</v>
+        <v>0.01279045445723416</v>
       </c>
       <c r="N13" t="n">
-        <v>1.001824767484191</v>
+        <v>1.000194526503275</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1966840141999172</v>
+        <v>0.0133349705833694</v>
       </c>
       <c r="P13" t="n">
-        <v>194.6713905252556</v>
+        <v>133.4362245271667</v>
       </c>
       <c r="Q13" t="n">
-        <v>309.2457180628664</v>
+        <v>204.1310223695223</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9949303074306233</v>
+        <v>0.9997273169990423</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7103348554006875</v>
+        <v>0.6228303751246184</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9644728675492253</v>
+        <v>0.9990171321072522</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9903899303491862</v>
+        <v>0.9997171131826776</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9878185783933632</v>
+        <v>0.9993818794764522</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03390105755521019</v>
+        <v>0.000161876408660818</v>
       </c>
       <c r="H14" t="n">
-        <v>1.936992155720952</v>
+        <v>0.2239041822054644</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05774482178594137</v>
+        <v>0.0007808218319358567</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1378959927835293</v>
+        <v>0.0002142939105118144</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09782045889956104</v>
+        <v>0.0004975578712238356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2228429049469148</v>
+        <v>0.005811062371147416</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1841223982985508</v>
+        <v>0.01272306600866387</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001738180309501</v>
+        <v>1.000192482118323</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1919608699800283</v>
+        <v>0.01326471326903016</v>
       </c>
       <c r="P14" t="n">
-        <v>194.7686181375269</v>
+        <v>133.4573548467931</v>
       </c>
       <c r="Q14" t="n">
-        <v>309.3429456751377</v>
+        <v>204.1521526891487</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9951886761780897</v>
+        <v>0.999730197485062</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7101569574199051</v>
+        <v>0.6227488337141076</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9671144548978853</v>
+        <v>0.9990463704034585</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9911085916531417</v>
+        <v>0.999705696335818</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9887280023790564</v>
+        <v>0.9993909355374855</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03217334455122318</v>
+        <v>0.0001601664277290103</v>
       </c>
       <c r="H15" t="n">
-        <v>1.938181760337588</v>
+        <v>0.2239525887091491</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05345125852434923</v>
+        <v>0.000757593990051001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1275838392211825</v>
+        <v>0.0002229424604245878</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09051751229057797</v>
+        <v>0.0004902681691710499</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2191588109156063</v>
+        <v>0.005879730442311254</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1793692965677883</v>
+        <v>0.01265568756445142</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001649596738941</v>
+        <v>1.000190448834074</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1870054188683102</v>
+        <v>0.01319446638495498</v>
       </c>
       <c r="P15" t="n">
-        <v>194.8732339564461</v>
+        <v>133.4785942200591</v>
       </c>
       <c r="Q15" t="n">
-        <v>309.4475614940569</v>
+        <v>204.1733920624147</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9954482592447164</v>
+        <v>0.999732988810243</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7099395365417518</v>
+        <v>0.6226571761471602</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9699220003632538</v>
+        <v>0.9990777571961734</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9918741662160494</v>
+        <v>0.9996928071953605</v>
       </c>
       <c r="F16" t="n">
-        <v>0.989696106375783</v>
+        <v>0.9994003588938206</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03043751138942068</v>
+        <v>0.0001585093765225791</v>
       </c>
       <c r="H16" t="n">
-        <v>1.939635654750931</v>
+        <v>0.2240070006002898</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04888795151446711</v>
+        <v>0.0007326593135119225</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1165985219198626</v>
+        <v>0.0002327063099313163</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08274334764211949</v>
+        <v>0.0004826828117216194</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2150840980419527</v>
+        <v>0.005955111887457739</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1744634958649536</v>
+        <v>0.01259005069579067</v>
       </c>
       <c r="N16" t="n">
-        <v>1.001560596830383</v>
+        <v>1.000188478486887</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1818907680731484</v>
+        <v>0.01312603521890829</v>
       </c>
       <c r="P16" t="n">
-        <v>194.984159007898</v>
+        <v>133.4993936170511</v>
       </c>
       <c r="Q16" t="n">
-        <v>309.5584865455088</v>
+        <v>204.1941914594067</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9957027947265423</v>
+        <v>0.999735599068369</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7096734697224094</v>
+        <v>0.6225541191359466</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9728851984834179</v>
+        <v>0.9991112639665971</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9926841629618894</v>
+        <v>0.99967828633031</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9907196892528221</v>
+        <v>0.9994100594478135</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02873543145042208</v>
+        <v>0.0001569598145417402</v>
       </c>
       <c r="H17" t="n">
-        <v>1.941414844796999</v>
+        <v>0.2240681796939773</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04407165097001994</v>
+        <v>0.0007060404585697237</v>
       </c>
       <c r="J17" t="n">
-        <v>0.104975785615388</v>
+        <v>0.0002437062320385287</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07452367099131341</v>
+        <v>0.0004748743232303405</v>
       </c>
       <c r="L17" t="n">
-        <v>0.210576908314355</v>
+        <v>0.006037191538097317</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1695152838254477</v>
+        <v>0.0125283604091573</v>
       </c>
       <c r="N17" t="n">
-        <v>1.001473327522328</v>
+        <v>1.00018663595174</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1767319004029097</v>
+        <v>0.01306171864905644</v>
       </c>
       <c r="P17" t="n">
-        <v>195.0992487446603</v>
+        <v>133.5190414874235</v>
       </c>
       <c r="Q17" t="n">
-        <v>309.6735762822711</v>
+        <v>204.2138393297791</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9959438204473094</v>
+        <v>0.9997379049155377</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7093474284206591</v>
+        <v>0.6224382734698626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9759852884871417</v>
+        <v>0.9991468982795272</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9935339971749692</v>
+        <v>0.9996618736222277</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9917926831397516</v>
+        <v>0.9994199220164797</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02712369134583143</v>
+        <v>0.0001555909640549525</v>
       </c>
       <c r="H18" t="n">
-        <v>1.943595084483084</v>
+        <v>0.2241369506856369</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03903285013143695</v>
+        <v>0.0006777314155058604</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09278141691962023</v>
+        <v>0.0002561392730346445</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06590720915251717</v>
+        <v>0.0004669354205675186</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2055895802377581</v>
+        <v>0.006126673408796358</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1646927179502222</v>
+        <v>0.01247361070640544</v>
       </c>
       <c r="N18" t="n">
-        <v>1.001390690132351</v>
+        <v>1.000185008294915</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1717040279142883</v>
+        <v>0.01300463813811093</v>
       </c>
       <c r="P18" t="n">
-        <v>195.2146954272006</v>
+        <v>133.5365600390649</v>
       </c>
       <c r="Q18" t="n">
-        <v>309.7890229648115</v>
+        <v>204.2313578814206</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9961600801815126</v>
+        <v>0.9997397409021175</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7089473322363755</v>
+        <v>0.6223077005687435</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9791946355571826</v>
+        <v>0.9991845403210786</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9944162406480471</v>
+        <v>0.9996433372902371</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9929057110401229</v>
+        <v>0.9994297744882987</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02567756150743005</v>
+        <v>0.0001545010431106822</v>
       </c>
       <c r="H19" t="n">
-        <v>1.946270529509663</v>
+        <v>0.2242144644001969</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03381646586891537</v>
+        <v>0.000647827368320239</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08012200403112182</v>
+        <v>0.0002701810127891379</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0569692622118236</v>
+        <v>0.0004590046453904281</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2000790609280101</v>
+        <v>0.006224029377003096</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1602421964010418</v>
+        <v>0.01242984485465053</v>
       </c>
       <c r="N19" t="n">
-        <v>1.001316543937767</v>
+        <v>1.000183712304388</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1670640384489096</v>
+        <v>0.012959009083439</v>
       </c>
       <c r="P19" t="n">
-        <v>195.3242755230897</v>
+        <v>133.5506194202476</v>
       </c>
       <c r="Q19" t="n">
-        <v>309.8986030607005</v>
+        <v>204.2454172626033</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9963369308256017</v>
+        <v>0.9997409176963631</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7084557201756529</v>
+        <v>0.6221606663998946</v>
       </c>
       <c r="D20" t="n">
-        <v>0.982473450155936</v>
+        <v>0.9992240716691636</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9953200636443447</v>
+        <v>0.9996223658276877</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9940450458038764</v>
+        <v>0.9994394139367632</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02449496043608382</v>
+        <v>0.0001538024472116732</v>
       </c>
       <c r="H20" t="n">
-        <v>1.94955794162338</v>
+        <v>0.2243017502343709</v>
       </c>
       <c r="I20" t="n">
-        <v>0.02848717100008517</v>
+        <v>0.0006164223953239287</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06715294408632978</v>
+        <v>0.000286067425459053</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0478200632899288</v>
+        <v>0.0004512453439677918</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1939978958571824</v>
+        <v>0.006329573611094549</v>
       </c>
       <c r="M20" t="n">
-        <v>0.15650865930064</v>
+        <v>0.01240171146300676</v>
       </c>
       <c r="N20" t="n">
-        <v>1.001255909431222</v>
+        <v>1.000182881626097</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1631715569446565</v>
+        <v>0.0129296779950688</v>
       </c>
       <c r="P20" t="n">
-        <v>195.4185757581525</v>
+        <v>133.5596831787399</v>
       </c>
       <c r="Q20" t="n">
-        <v>309.9929032957633</v>
+        <v>204.2544810210955</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9964552917533874</v>
+        <v>0.9997411846724222</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7078509701058642</v>
+        <v>0.6219949363007968</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9857659117318771</v>
+        <v>0.999265316107265</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9962300125955498</v>
+        <v>0.9995986069327042</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9951912372174514</v>
+        <v>0.9994485881564434</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02370348036697883</v>
+        <v>0.0001536439586901485</v>
       </c>
       <c r="H21" t="n">
-        <v>1.953601908124675</v>
+        <v>0.2244001347803629</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02313569471071109</v>
+        <v>0.0005836564885799299</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05409598211122602</v>
+        <v>0.0003040653886149738</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03861580341917947</v>
+        <v>0.0004438605297764599</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1872926612430228</v>
+        <v>0.006444015531258356</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1539593464749017</v>
+        <v>0.01239532003177604</v>
       </c>
       <c r="N21" t="n">
-        <v>1.001215328541696</v>
+        <v>1.000182693172408</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1605137145941214</v>
+        <v>0.01292301446737852</v>
       </c>
       <c r="P21" t="n">
-        <v>195.4842667813904</v>
+        <v>133.5617451776122</v>
       </c>
       <c r="Q21" t="n">
-        <v>310.0585943190013</v>
+        <v>204.2565430199678</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9964907192398077</v>
+        <v>0.9997402236616977</v>
       </c>
       <c r="C22" t="n">
-        <v>0.70710614909764</v>
+        <v>0.6218081716259234</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9889980148615829</v>
+        <v>0.9993078880891241</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9971248740508108</v>
+        <v>0.9995716939411878</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9963178269614356</v>
+        <v>0.9994569317969442</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02346657660215768</v>
+        <v>0.0001542144561697963</v>
       </c>
       <c r="H22" t="n">
-        <v>1.958582529636256</v>
+        <v>0.2245110063591816</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0178823233760771</v>
+        <v>0.00054983593842299</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04125551234767166</v>
+        <v>0.0003244526595744238</v>
       </c>
       <c r="K22" t="n">
-        <v>0.02956895081799978</v>
+        <v>0.0004371442926549302</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1799130782031997</v>
+        <v>0.006577923505352305</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1531880432741331</v>
+        <v>0.01241831132520829</v>
       </c>
       <c r="N22" t="n">
-        <v>1.001203181974923</v>
+        <v>1.000183371532919</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1597095754192784</v>
+        <v>0.01294698454777071</v>
       </c>
       <c r="P22" t="n">
-        <v>195.5043562849397</v>
+        <v>133.5543327034988</v>
       </c>
       <c r="Q22" t="n">
-        <v>310.0786838225505</v>
+        <v>204.2491305458544</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9964119015622769</v>
+        <v>0.9997376499283711</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7061878248923705</v>
+        <v>0.6215974097159398</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9920711334260298</v>
+        <v>0.9993514326535263</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9979760223152443</v>
+        <v>0.9995411201174619</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9973892878735779</v>
+        <v>0.9994640328366036</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0239936307747283</v>
+        <v>0.0001557423354519103</v>
       </c>
       <c r="H23" t="n">
-        <v>1.964723367825387</v>
+        <v>0.2246361237333883</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01288736117143148</v>
+        <v>0.0005152427374462158</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0290422881781568</v>
+        <v>0.000347613103413911</v>
       </c>
       <c r="K23" t="n">
-        <v>0.02096479922524939</v>
+        <v>0.0004314282906103715</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1718008621114412</v>
+        <v>0.006738866137672396</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1548987758980951</v>
+        <v>0.01247967689693568</v>
       </c>
       <c r="N23" t="n">
-        <v>1.001230205178648</v>
+        <v>1.000185188285856</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1614931374727472</v>
+        <v>0.01301096257893079</v>
       </c>
       <c r="P23" t="n">
-        <v>195.4599337364824</v>
+        <v>133.5346152241785</v>
       </c>
       <c r="Q23" t="n">
-        <v>310.0342612740932</v>
+        <v>204.2294130665341</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9961792786286338</v>
+        <v>0.9997329916949281</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7050545093983022</v>
+        <v>0.6213594441623251</v>
       </c>
       <c r="D24" t="n">
-        <v>0.994859591084392</v>
+        <v>0.9993953512341583</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9987457188055502</v>
+        <v>0.9995064281114203</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9983591564335342</v>
+        <v>0.9994693815976953</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02554918140313049</v>
+        <v>0.0001585076640488889</v>
       </c>
       <c r="H24" t="n">
-        <v>1.97230185375266</v>
+        <v>0.2247773903655907</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00835507895690514</v>
+        <v>0.0004803524059600037</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01799782486734904</v>
+        <v>0.0003738931743925275</v>
       </c>
       <c r="K24" t="n">
-        <v>0.01317646460628445</v>
+        <v>0.0004271227901762656</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1628968067787616</v>
+        <v>0.006914759218810152</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1598411129939056</v>
+        <v>0.01258998268660005</v>
       </c>
       <c r="N24" t="n">
-        <v>1.00130996161304</v>
+        <v>1.000188476450639</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1666458800907745</v>
+        <v>0.01312596431442562</v>
       </c>
       <c r="P24" t="n">
-        <v>195.3343000037242</v>
+        <v>133.4994152243904</v>
       </c>
       <c r="Q24" t="n">
-        <v>309.908627541335</v>
+        <v>204.194213066746</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9957428466049177</v>
+        <v>0.9997256602757321</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7036545004268071</v>
+        <v>0.6210909791378916</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9972029096200394</v>
+        <v>0.9994389719864998</v>
       </c>
       <c r="E25" t="n">
-        <v>0.999384679616649</v>
+        <v>0.9994669490153826</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9991671774044508</v>
+        <v>0.9994723302459628</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02846760435530372</v>
+        <v>0.0001628599111844686</v>
       </c>
       <c r="H25" t="n">
-        <v>1.981663720191496</v>
+        <v>0.2249367628011797</v>
       </c>
       <c r="I25" t="n">
-        <v>0.004546313602252773</v>
+        <v>0.0004456986788365549</v>
       </c>
       <c r="J25" t="n">
-        <v>0.008829302827679053</v>
+        <v>0.0004037995869765083</v>
       </c>
       <c r="K25" t="n">
-        <v>0.006687814535058671</v>
+        <v>0.0004247492673775573</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1531792505936706</v>
+        <v>0.007106931734662282</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1687234552612758</v>
+        <v>0.01276165785407478</v>
       </c>
       <c r="N25" t="n">
-        <v>1.001459595449743</v>
+        <v>1.000193651570072</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1759063620574499</v>
+        <v>0.01330494804919635</v>
       </c>
       <c r="P25" t="n">
-        <v>195.1179770550327</v>
+        <v>133.4452403345488</v>
       </c>
       <c r="Q25" t="n">
-        <v>309.6923045926436</v>
+        <v>204.1400381769044</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9950398788008485</v>
+        <v>0.9997149515153023</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7019236749064623</v>
+        <v>0.6207879270986794</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9989002717669466</v>
+        <v>0.9994813561510634</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9998292611142517</v>
+        <v>0.9994220759787935</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9997361607558474</v>
+        <v>0.9994721306864748</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03316835329798363</v>
+        <v>0.0001692170939699282</v>
       </c>
       <c r="H26" t="n">
-        <v>1.99323775841576</v>
+        <v>0.2251166675828225</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001787467956177583</v>
+        <v>0.0004120273367734185</v>
       </c>
       <c r="J26" t="n">
-        <v>0.002449951874700196</v>
+        <v>0.0004377920457917823</v>
       </c>
       <c r="K26" t="n">
-        <v>0.002118708043457366</v>
+        <v>0.0004249099033543088</v>
       </c>
       <c r="L26" t="n">
-        <v>0.142581381559435</v>
+        <v>0.007317085407132346</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1821218089575865</v>
+        <v>0.01300834708830942</v>
       </c>
       <c r="N26" t="n">
-        <v>1.001700612982566</v>
+        <v>1.000201210695081</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1898751114090283</v>
+        <v>0.01356213935484947</v>
       </c>
       <c r="P26" t="n">
-        <v>194.8123181431463</v>
+        <v>133.3686561754082</v>
       </c>
       <c r="Q26" t="n">
-        <v>309.3866456807571</v>
+        <v>204.0634540177638</v>
       </c>
     </row>
   </sheetData>
